--- a/jogos_2025-02-13.xlsx
+++ b/jogos_2025-02-13.xlsx
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.22</v>
+        <v>3.63</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.73</v>
+        <v>4.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>2.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="X4" t="n">
-        <v>3.05</v>
+        <v>2.17</v>
       </c>
       <c r="Y4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.85</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['45', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45701.41666666666</v>
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.63</v>
+        <v>1.22</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
-        <v>4.6</v>
+        <v>1.73</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>11</v>
       </c>
       <c r="R7" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="U7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['45', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1.2</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>1.85</v>
+        <v>6</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45701.41666666666</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="W25" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="X25" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="Z25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.44</v>
       </c>
-      <c r="AA25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44', '90+1']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.66</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45701.83333333334</v>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X26" t="n">
         <v>2.25</v>
       </c>
-      <c r="M26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R26" t="n">
+      <c r="Y26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>1.73</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>5</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['44', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45701.83333333334</v>
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.63</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="P29" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
+        <v>6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T29" t="n">
         <v>4</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>4.33</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.15</v>
       </c>
-      <c r="W29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
+          <t>['2', '30', '42', '45', '67']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG29" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.49</v>
+        <v>1.93</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45701.92708333334</v>
@@ -4255,91 +4255,91 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q30" t="n">
         <v>4</v>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6</v>
-      </c>
       <c r="R30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.62</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>4</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.12</v>
       </c>
-      <c r="W30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AC30" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['2', '30', '42', '45', '67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45701.92708333334</v>
